--- a/reports/二级子公司C_利润表_2026-06.xlsx
+++ b/reports/二级子公司C_利润表_2026-06.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>93518335</v>
+        <v>96053011</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>90813040</v>
+        <v>91252540</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>488417760</v>
+        <v>488016563</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>424360</v>
+        <v>422646</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2397840</v>
+        <v>2401101</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>371315</v>
+        <v>369272</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2098110</v>
+        <v>2100240</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>318270</v>
+        <v>316361</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1798380</v>
+        <v>1799263</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>297052</v>
+        <v>295436</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1678488</v>
+        <v>1678288</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>159135</v>
+        <v>158511</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>899190</v>
+        <v>898553</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>127308</v>
+        <v>127089</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>719352</v>
+        <v>718508</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>91820895</v>
+        <v>94363696</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>89115600</v>
+        <v>89563225</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>84872000</v>
+        <v>85294283</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>454848000</v>
+        <v>454425233</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1273080</v>
+        <v>1280608</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>7193520</v>
+        <v>7188234</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>848720</v>
+        <v>853651</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>4795680</v>
+        <v>4794963</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>3182700</v>
+        <v>3197610</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>17983800</v>
+        <v>17992114</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>424360</v>
+        <v>425521</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>2397840</v>
+        <v>2400221</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>318270</v>
+        <v>318367</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1798380</v>
+        <v>1800805</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>530450</v>
+        <v>529293</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>2997300</v>
+        <v>3001695</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>636540</v>
+        <v>633815</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>3596760</v>
+        <v>3601532</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>2652250</v>
+        <v>2637321</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>14986500</v>
+        <v>15000793</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>53045</v>
+        <v>51192</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>299730</v>
+        <v>309196</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1266346</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>7192074</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>845612</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>4791943</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>63388775</v>
+        <v>68151054</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>56439880</v>
+        <v>56636443</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>55166800</v>
+        <v>55356799</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>311719200</v>
+        <v>311276998</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>1273080</v>
+        <v>1279644</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>7193520</v>
+        <v>7185313</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>2134448</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>11981260</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>682858</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>3836286</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>426255</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>2399134</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>510470</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2880434</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>381911</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2161031</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>253982</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1440809</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>211223</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1200467</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>954810</v>
+        <v>949333</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>5395140</v>
+        <v>5399940</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>742630</v>
+        <v>738209</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>4196220</v>
+        <v>4197617</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>636540</v>
+        <v>633280</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>3596760</v>
+        <v>3595745</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4774050</v>
+        <v>4757871</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>26975700</v>
+        <v>26952831</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>212180</v>
+        <v>211955</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1198920</v>
+        <v>1197404</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>371315</v>
+        <v>361025</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2098110</v>
+        <v>2160155</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>424360</v>
+        <v>361025</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>2397840</v>
+        <v>2160155</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>53045</v>
+        <v>51774</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>299730</v>
+        <v>308636</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>186511</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1111530</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>373396</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2098142</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>124123</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>741844</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>92896</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>556671</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>154443</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>928130</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>528968</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>3001659</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>82011</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>495037</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>61440</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>371162</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>102392</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>618304</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>71744</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>432566</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>51340</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>308802</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>41170</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>246933</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>30955</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>185153</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>28432120</v>
+        <v>27506045</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>33259215</v>
+        <v>31030220</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>213453</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1198308</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>51782</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>308947</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>84872</v>
+        <v>82729</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>479568</v>
+        <v>494599</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>28347248</v>
+        <v>27636769</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2970520</v>
+        <v>2881961</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>16784880</v>
+        <v>17325669</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>25376728</v>
+        <v>24754808</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>25376728</v>
+        <v>24754808</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>25376728</v>
+        <v>24754808</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>25376728</v>
+        <v>24754808</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>25376728</v>
+        <v>24754808</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
